--- a/data/mathias_msi_missions.xlsx
+++ b/data/mathias_msi_missions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JES\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D62C57B-23D7-4B8F-99B3-8B31A7791EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63249DC-5F67-4351-A7BC-AA21BA917760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{A3D75682-D577-4F07-A6EA-A76A63C4E592}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>H20</t>
   </si>
@@ -164,18 +164,6 @@
     <t>comment</t>
   </si>
   <si>
-    <t>Some outputs present, but 'pix4d_orthophoto.original.tif' (i.e. the mosaic) is missing</t>
-  </si>
-  <si>
-    <t>Mosaic has 6 bands instead of 5. Band order unclear.</t>
-  </si>
-  <si>
-    <t>Pix4D mosaic uploaded with a different name?</t>
-  </si>
-  <si>
-    <t>Pix4D output is a single-band greyscale GeoTIFF, not an MSI datset?</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -186,13 +174,73 @@
   </si>
   <si>
     <t>niva-tidy/2023/niva_202308290812_halden_h37_msi_70</t>
+  </si>
+  <si>
+    <t>dsm_path</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308301149_halden_h20_rgb_80/orthophoto/niva_202308301149_halden_h20_rgb_80/3_dsm_ortho/1_dsm/niva_202308301149_halden_h20_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308301109_halden_h21_rgb_80/orthophoto/niva_202308301109_halden_h21_rgb_80/3_dsm_ortho/1_dsm/niva_202308301109_halden_h21_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308300741_halden_h22_rgb_80/orthophoto/niva_202308300741_halden_h22_rgb_80/3_dsm_ortho/1_dsm/niva_202308300741_halden_h22_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308301032_halden_h23_rgb_80/orthophoto/niva_202308301032_halden_h23_rgb_80/3_dsm_ortho/1_dsm/niva_202308301032_halden_h23_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308291354_halden_h24_rgb_80/orthophoto/niva_202308291354_halden_h24_rgb_80/3_dsm_ortho/1_dsm/niva_202308291354_halden_h24_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308291253_halden_h25_rgb_80/orthophoto/niva_202308291253_halden_h25_rgb_80/3_dsm_ortho/1_dsm/niva_202308291253_halden_h25_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308291429_halden_h28_rgb_80/orthophoto/niva_202308291429_halden_h28_rgb_80/3_dsm_ortho/1_dsm/niva_202308291429_halden_h28_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308290947_halden_h29_rgb_80/orthophoto/niva_202308290947_halden_h29_rgb_80/3_dsm_ortho/1_dsm/niva_202308290947_halden_h29_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308291046_halden_h30_rgb_80/orthophoto/niva_202308291046_halden_h30_rgb_80/3_dsm_ortho/1_dsm/niva_202308291046_halden_h30_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308291127_halden_h31_rgb_80/orthophoto/niva_202308291127_halden_h31_rgb_80/3_dsm_ortho/1_dsm/niva_202308291127_halden_h31_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308300943_halden_h33_rgb_80/orthophoto/niva_202308300943_halden_h33_rgb_80/3_dsm_ortho/1_dsm/niva_202308300943_halden_h33_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308300859_halden_h34_rgb_80/orthophoto/niva_202308300859_halden_h34_rgb_80/3_dsm_ortho/1_dsm/niva_202308300859_halden_h34_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308300813_halden_h35_rgb_80/orthophoto/niva_202308300813_halden_h35_rgb_80/3_dsm_ortho/1_dsm/niva_202308300813_halden_h35_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308290755_halden_h37_rgb_80/orthophoto/niva_202308290755_h37_rgb_80/3_dsm_ortho/1_dsm/niva_202308290755_h37_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-tidy/2023/niva_202308290849_halden_h36_rgb_80/orthophoto/niva_202308290849_halden_h36_rgb_80/3_dsm_ortho/1_dsm/niva_202308290849_halden_h36_rgb_80_dsm.tif</t>
+  </si>
+  <si>
+    <t>niva-sabicas_halden-h33_202308300956_msi_80m</t>
+  </si>
+  <si>
+    <t>niva-sabicas_halden-h34_202308300910_msi_80m</t>
+  </si>
+  <si>
+    <t>niva-sabicas_halden-h35_202308300823_msi_80m</t>
+  </si>
+  <si>
+    <t>niva-sabicas_halden-h37_202308290812_msi_70m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +259,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -234,10 +288,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,17 +627,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6E4EEC-8A4A-4B81-9747-01C8A0801B8A}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="172.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -593,10 +649,13 @@
         <v>40</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,11 +665,14 @@
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -620,11 +682,14 @@
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -634,11 +699,14 @@
       <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -648,11 +716,14 @@
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -662,11 +733,14 @@
       <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -676,11 +750,14 @@
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -690,11 +767,14 @@
       <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -704,11 +784,14 @@
       <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -718,11 +801,14 @@
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -732,44 +818,65 @@
       <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -779,19 +886,28 @@
       <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
